--- a/XLibur.Tests/Resource/Examples/Tables/InsertingTables.xlsx
+++ b/XLibur.Tests/Resource/Examples/Tables/InsertingTables.xlsx
@@ -583,11 +583,12 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="12.424911" style="0" customWidth="1"/>
-    <x:col min="2" max="5" width="11.282054" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="14.853482" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="11.424911" style="0" customWidth="1"/>
+    <x:col min="3" max="5" width="11.282054" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="14.996339" style="0" customWidth="1"/>
     <x:col min="7" max="7" width="12.424911" style="0" customWidth="1"/>
     <x:col min="8" max="8" width="11.282054" style="0" customWidth="1"/>
-    <x:col min="9" max="9" width="6.424911" style="0" customWidth="1"/>
+    <x:col min="9" max="9" width="6.567768" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:9">

--- a/XLibur.Tests/Resource/Examples/Tables/InsertingTables.xlsx
+++ b/XLibur.Tests/Resource/Examples/Tables/InsertingTables.xlsx
@@ -582,7 +582,7 @@
   <x:dimension ref="A1:I19"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="12.424911" style="0" customWidth="1"/>
+    <x:col min="1" max="1" width="12.567768" style="0" customWidth="1"/>
     <x:col min="2" max="2" width="11.424911" style="0" customWidth="1"/>
     <x:col min="3" max="5" width="11.282054" style="0" customWidth="1"/>
     <x:col min="6" max="6" width="14.996339" style="0" customWidth="1"/>
